--- a/xlsx/換色紀錄表(2502) 3號盤存.xlsx
+++ b/xlsx/換色紀錄表(2502) 3號盤存.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d310cb6cf3413c87/換色紀錄表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{F0BA7AB4-E329-474E-9B64-75E57F7D63BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{37D1D6A4-92A2-2D41-8771-E9D1B0538619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2960,13 +2960,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表格2" displayName="表格2" ref="B2:O123" headerRowDxfId="78" headerRowBorderDxfId="77" tableBorderDxfId="76" totalsRowBorderDxfId="75">
-  <autoFilter ref="B2:O123" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="DP-11485"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="B2:O123" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="日期" dataDxfId="74"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="粉號" dataDxfId="73"/>
@@ -5366,7 +5360,7 @@
       <c r="N3" s="27"/>
       <c r="O3" s="27"/>
     </row>
-    <row r="4" spans="1:257" hidden="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A4" s="125" t="e" cm="1">
         <f t="array" aca="1" ref="A4" ca="1">--mlt</f>
         <v>#NAME?</v>
@@ -5408,7 +5402,7 @@
       <c r="N4" s="27"/>
       <c r="O4" s="27"/>
     </row>
-    <row r="5" spans="1:257" hidden="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A5" s="125"/>
       <c r="B5" s="121">
         <v>45692</v>
@@ -5447,7 +5441,7 @@
       <c r="N5" s="27"/>
       <c r="O5" s="27"/>
     </row>
-    <row r="6" spans="1:257" hidden="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A6" s="125"/>
       <c r="B6" s="121">
         <v>45692</v>
@@ -5488,7 +5482,7 @@
       <c r="N6" s="27"/>
       <c r="O6" s="27"/>
     </row>
-    <row r="7" spans="1:257" hidden="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A7" s="125"/>
       <c r="B7" s="121">
         <v>45692</v>
@@ -5529,7 +5523,7 @@
       <c r="N7" s="27"/>
       <c r="O7" s="27"/>
     </row>
-    <row r="8" spans="1:257" hidden="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A8" s="125"/>
       <c r="B8" s="121">
         <v>45693</v>
@@ -5562,7 +5556,7 @@
       <c r="N8" s="27"/>
       <c r="O8" s="27"/>
     </row>
-    <row r="9" spans="1:257" hidden="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A9" s="125"/>
       <c r="B9" s="121">
         <v>45694</v>
@@ -5636,7 +5630,7 @@
       <c r="N10" s="27"/>
       <c r="O10" s="27"/>
     </row>
-    <row r="11" spans="1:257" hidden="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A11" s="125"/>
       <c r="B11" s="121">
         <v>45694</v>
@@ -5673,7 +5667,7 @@
       <c r="N11" s="27"/>
       <c r="O11" s="27"/>
     </row>
-    <row r="12" spans="1:257" hidden="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A12" s="125"/>
       <c r="B12" s="121">
         <v>45694</v>
@@ -5710,7 +5704,7 @@
       <c r="N12" s="27"/>
       <c r="O12" s="27"/>
     </row>
-    <row r="13" spans="1:257" hidden="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A13" s="125"/>
       <c r="B13" s="121">
         <v>45695</v>
@@ -5747,7 +5741,7 @@
       <c r="N13" s="27"/>
       <c r="O13" s="27"/>
     </row>
-    <row r="14" spans="1:257" hidden="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:257" x14ac:dyDescent="0.15">
       <c r="A14" s="125"/>
       <c r="B14" s="121">
         <v>45695</v>
@@ -5856,7 +5850,7 @@
       <c r="N16" s="27"/>
       <c r="O16" s="27"/>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A17" s="125" t="s">
         <v>35</v>
       </c>
@@ -5891,7 +5885,7 @@
       <c r="N17" s="27"/>
       <c r="O17" s="27"/>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A18" s="125"/>
       <c r="B18" s="121">
         <v>45698</v>
@@ -5928,7 +5922,7 @@
       <c r="N18" s="27"/>
       <c r="O18" s="27"/>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A19" s="125"/>
       <c r="B19" s="121">
         <v>45698</v>
@@ -5965,7 +5959,7 @@
       <c r="N19" s="27"/>
       <c r="O19" s="27"/>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A20" s="125"/>
       <c r="B20" s="121">
         <v>45698</v>
@@ -6072,7 +6066,7 @@
       <c r="N22" s="27"/>
       <c r="O22" s="27"/>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A23" s="125"/>
       <c r="B23" s="121">
         <v>45700</v>
@@ -6140,7 +6134,7 @@
       <c r="N24" s="27"/>
       <c r="O24" s="27"/>
     </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A25" s="125"/>
       <c r="B25" s="121">
         <v>45701</v>
@@ -6173,7 +6167,7 @@
       <c r="N25" s="27"/>
       <c r="O25" s="27"/>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A26" s="125"/>
       <c r="B26" s="121">
         <v>45702</v>
@@ -6245,7 +6239,7 @@
       <c r="N27" s="27"/>
       <c r="O27" s="27"/>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A28" s="125"/>
       <c r="B28" s="121">
         <v>45703</v>
@@ -6278,7 +6272,7 @@
       <c r="N28" s="27"/>
       <c r="O28" s="27"/>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A29" s="125"/>
       <c r="B29" s="121">
         <v>45704</v>
@@ -6311,7 +6305,7 @@
       <c r="N29" s="27"/>
       <c r="O29" s="27"/>
     </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A30" s="125"/>
       <c r="B30" s="121">
         <v>45705</v>
@@ -6344,7 +6338,7 @@
       <c r="N30" s="27"/>
       <c r="O30" s="27"/>
     </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A31" s="125"/>
       <c r="B31" s="121">
         <v>45705</v>
@@ -6381,7 +6375,7 @@
       <c r="N31" s="27"/>
       <c r="O31" s="27"/>
     </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A32" s="125"/>
       <c r="B32" s="121">
         <v>45705</v>
@@ -6418,7 +6412,7 @@
       <c r="N32" s="27"/>
       <c r="O32" s="27"/>
     </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A33" s="125"/>
       <c r="B33" s="121">
         <v>45705</v>
@@ -6455,7 +6449,7 @@
       <c r="N33" s="27"/>
       <c r="O33" s="27"/>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A34" s="125"/>
       <c r="B34" s="121">
         <v>45705</v>
@@ -6492,7 +6486,7 @@
       <c r="N34" s="27"/>
       <c r="O34" s="27"/>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A35" s="125"/>
       <c r="B35" s="121">
         <v>45706</v>
@@ -6529,7 +6523,7 @@
       <c r="N35" s="27"/>
       <c r="O35" s="27"/>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A36" s="125"/>
       <c r="B36" s="121">
         <v>45706</v>
@@ -6564,7 +6558,7 @@
       <c r="N36" s="27"/>
       <c r="O36" s="27"/>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A37" s="125"/>
       <c r="B37" s="121">
         <v>45706</v>
@@ -6597,7 +6591,7 @@
       <c r="N37" s="27"/>
       <c r="O37" s="27"/>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A38" s="125"/>
       <c r="B38" s="121">
         <v>45706</v>
@@ -6634,7 +6628,7 @@
       <c r="N38" s="27"/>
       <c r="O38" s="27"/>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A39" s="125"/>
       <c r="B39" s="121">
         <v>45707</v>
@@ -6667,7 +6661,7 @@
       <c r="N39" s="27"/>
       <c r="O39" s="27"/>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A40" s="125"/>
       <c r="B40" s="121">
         <v>45708</v>
@@ -6704,7 +6698,7 @@
       <c r="N40" s="27"/>
       <c r="O40" s="27"/>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A41" s="125"/>
       <c r="B41" s="121">
         <v>45708</v>
@@ -6741,7 +6735,7 @@
       <c r="N41" s="27"/>
       <c r="O41" s="27"/>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A42" s="125"/>
       <c r="B42" s="121">
         <v>45708</v>
@@ -6811,7 +6805,7 @@
       <c r="N43" s="27"/>
       <c r="O43" s="27"/>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A44" s="125"/>
       <c r="B44" s="121">
         <v>45709</v>
@@ -6844,7 +6838,7 @@
       <c r="N44" s="27"/>
       <c r="O44" s="27"/>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A45" s="125"/>
       <c r="B45" s="158">
         <v>45710</v>
@@ -6877,7 +6871,7 @@
       <c r="N45" s="27"/>
       <c r="O45" s="27"/>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A46" s="125"/>
       <c r="B46" s="158">
         <v>45711</v>
@@ -6945,7 +6939,7 @@
       <c r="N47" s="27"/>
       <c r="O47" s="27"/>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A48" s="125"/>
       <c r="B48" s="158">
         <v>45712</v>
@@ -6978,7 +6972,7 @@
       <c r="N48" s="27"/>
       <c r="O48" s="27"/>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A49" s="125"/>
       <c r="B49" s="158">
         <v>45713</v>
@@ -7120,7 +7114,7 @@
       <c r="N52" s="27"/>
       <c r="O52" s="27"/>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A53" s="125"/>
       <c r="B53" s="121">
         <v>45715</v>
@@ -7157,7 +7151,7 @@
       <c r="N53" s="27"/>
       <c r="O53" s="27"/>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A54" s="125"/>
       <c r="B54" s="121">
         <v>45719</v>
@@ -7194,7 +7188,7 @@
       <c r="N54" s="27"/>
       <c r="O54" s="27"/>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A55" s="125"/>
       <c r="B55" s="121">
         <v>45719</v>
@@ -7231,7 +7225,7 @@
       <c r="N55" s="27"/>
       <c r="O55" s="27"/>
     </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A56" s="125"/>
       <c r="B56" s="121">
         <v>45719</v>
@@ -7303,7 +7297,7 @@
       <c r="N57" s="27"/>
       <c r="O57" s="27"/>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A58" s="125"/>
       <c r="B58" s="121"/>
       <c r="C58" s="27"/>
@@ -7332,7 +7326,7 @@
       <c r="N58" s="27"/>
       <c r="O58" s="27"/>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A59" s="125"/>
       <c r="B59" s="121"/>
       <c r="C59" s="27"/>
@@ -7361,7 +7355,7 @@
       <c r="N59" s="27"/>
       <c r="O59" s="27"/>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A60" s="125"/>
       <c r="B60" s="121"/>
       <c r="C60" s="27"/>
@@ -7390,7 +7384,7 @@
       <c r="N60" s="27"/>
       <c r="O60" s="27"/>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A61" s="125"/>
       <c r="B61" s="121"/>
       <c r="C61" s="27"/>
@@ -7419,7 +7413,7 @@
       <c r="N61" s="27"/>
       <c r="O61" s="27"/>
     </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A62" s="125"/>
       <c r="B62" s="121"/>
       <c r="C62" s="27"/>
@@ -7448,7 +7442,7 @@
       <c r="N62" s="27"/>
       <c r="O62" s="27"/>
     </row>
-    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A63" s="125"/>
       <c r="B63" s="121"/>
       <c r="C63" s="27"/>
@@ -7477,7 +7471,7 @@
       <c r="N63" s="27"/>
       <c r="O63" s="27"/>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A64" s="125"/>
       <c r="B64" s="121"/>
       <c r="C64" s="27"/>
@@ -7506,7 +7500,7 @@
       <c r="N64" s="27"/>
       <c r="O64" s="27"/>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A65" s="125"/>
       <c r="B65" s="121"/>
       <c r="C65" s="27"/>
@@ -7535,7 +7529,7 @@
       <c r="N65" s="27"/>
       <c r="O65" s="27"/>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A66" s="125"/>
       <c r="B66" s="121"/>
       <c r="C66" s="27"/>
@@ -7564,7 +7558,7 @@
       <c r="N66" s="27"/>
       <c r="O66" s="27"/>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A67" s="125"/>
       <c r="B67" s="122"/>
       <c r="C67" s="34"/>
@@ -7593,7 +7587,7 @@
       <c r="N67" s="34"/>
       <c r="O67" s="34"/>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A68" s="125"/>
       <c r="B68" s="122"/>
       <c r="C68" s="34"/>
@@ -7622,7 +7616,7 @@
       <c r="N68" s="34"/>
       <c r="O68" s="34"/>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A69" s="125"/>
       <c r="B69" s="122"/>
       <c r="C69" s="34"/>
@@ -7651,7 +7645,7 @@
       <c r="N69" s="34"/>
       <c r="O69" s="34"/>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A70" s="125"/>
       <c r="B70" s="122"/>
       <c r="C70" s="34"/>
@@ -7680,7 +7674,7 @@
       <c r="N70" s="34"/>
       <c r="O70" s="34"/>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A71" s="125"/>
       <c r="B71" s="122"/>
       <c r="C71" s="34"/>
@@ -7709,7 +7703,7 @@
       <c r="N71" s="34"/>
       <c r="O71" s="34"/>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A72" s="125"/>
       <c r="B72" s="122"/>
       <c r="C72" s="34"/>
@@ -7738,7 +7732,7 @@
       <c r="N72" s="34"/>
       <c r="O72" s="34"/>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A73" s="125"/>
       <c r="B73" s="122"/>
       <c r="C73" s="34"/>
@@ -7767,7 +7761,7 @@
       <c r="N73" s="34"/>
       <c r="O73" s="34"/>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A74" s="125"/>
       <c r="B74" s="122"/>
       <c r="C74" s="34"/>
@@ -7796,7 +7790,7 @@
       <c r="N74" s="34"/>
       <c r="O74" s="34"/>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A75" s="125"/>
       <c r="B75" s="122"/>
       <c r="C75" s="34"/>
@@ -7825,7 +7819,7 @@
       <c r="N75" s="34"/>
       <c r="O75" s="34"/>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A76" s="125"/>
       <c r="B76" s="122"/>
       <c r="C76" s="34"/>
@@ -7854,7 +7848,7 @@
       <c r="N76" s="34"/>
       <c r="O76" s="34"/>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A77" s="125"/>
       <c r="B77" s="122"/>
       <c r="C77" s="34"/>
@@ -7883,7 +7877,7 @@
       <c r="N77" s="34"/>
       <c r="O77" s="34"/>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A78" s="125"/>
       <c r="B78" s="122"/>
       <c r="C78" s="34"/>
@@ -7912,7 +7906,7 @@
       <c r="N78" s="34"/>
       <c r="O78" s="34"/>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A79" s="125"/>
       <c r="B79" s="122"/>
       <c r="C79" s="34"/>
@@ -7941,7 +7935,7 @@
       <c r="N79" s="34"/>
       <c r="O79" s="34"/>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A80" s="125"/>
       <c r="B80" s="122"/>
       <c r="C80" s="34"/>
@@ -7970,7 +7964,7 @@
       <c r="N80" s="34"/>
       <c r="O80" s="34"/>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A81" s="125"/>
       <c r="B81" s="122"/>
       <c r="C81" s="34"/>
@@ -7999,7 +7993,7 @@
       <c r="N81" s="34"/>
       <c r="O81" s="34"/>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A82" s="125"/>
       <c r="B82" s="122"/>
       <c r="C82" s="34"/>
@@ -8028,7 +8022,7 @@
       <c r="N82" s="34"/>
       <c r="O82" s="34"/>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A83" s="125"/>
       <c r="B83" s="122"/>
       <c r="C83" s="34"/>
@@ -8057,7 +8051,7 @@
       <c r="N83" s="34"/>
       <c r="O83" s="34"/>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A84" s="125"/>
       <c r="B84" s="122"/>
       <c r="C84" s="34"/>
@@ -8086,7 +8080,7 @@
       <c r="N84" s="34"/>
       <c r="O84" s="34"/>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A85" s="125"/>
       <c r="B85" s="122"/>
       <c r="C85" s="34"/>
@@ -8115,7 +8109,7 @@
       <c r="N85" s="34"/>
       <c r="O85" s="34"/>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A86" s="125"/>
       <c r="B86" s="122"/>
       <c r="C86" s="34"/>
@@ -8144,7 +8138,7 @@
       <c r="N86" s="34"/>
       <c r="O86" s="34"/>
     </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A87" s="125"/>
       <c r="B87" s="122"/>
       <c r="C87" s="34"/>
@@ -8173,7 +8167,7 @@
       <c r="N87" s="34"/>
       <c r="O87" s="34"/>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A88" s="125"/>
       <c r="B88" s="122"/>
       <c r="C88" s="34"/>
@@ -8202,7 +8196,7 @@
       <c r="N88" s="34"/>
       <c r="O88" s="34"/>
     </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A89" s="125"/>
       <c r="B89" s="122"/>
       <c r="C89" s="34"/>
@@ -8231,7 +8225,7 @@
       <c r="N89" s="34"/>
       <c r="O89" s="34"/>
     </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A90" s="125"/>
       <c r="B90" s="122"/>
       <c r="C90" s="34"/>
@@ -8260,7 +8254,7 @@
       <c r="N90" s="34"/>
       <c r="O90" s="34"/>
     </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A91" s="125"/>
       <c r="B91" s="122"/>
       <c r="C91" s="34"/>
@@ -8289,7 +8283,7 @@
       <c r="N91" s="34"/>
       <c r="O91" s="34"/>
     </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A92" s="125"/>
       <c r="B92" s="122"/>
       <c r="C92" s="34"/>
@@ -8318,7 +8312,7 @@
       <c r="N92" s="34"/>
       <c r="O92" s="34"/>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A93" s="125"/>
       <c r="B93" s="122"/>
       <c r="C93" s="34"/>
@@ -8347,7 +8341,7 @@
       <c r="N93" s="34"/>
       <c r="O93" s="34"/>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A94" s="125"/>
       <c r="B94" s="122"/>
       <c r="C94" s="34"/>
@@ -8376,7 +8370,7 @@
       <c r="N94" s="34"/>
       <c r="O94" s="34"/>
     </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A95" s="125"/>
       <c r="B95" s="122"/>
       <c r="C95" s="34"/>
@@ -8405,7 +8399,7 @@
       <c r="N95" s="34"/>
       <c r="O95" s="34"/>
     </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A96" s="125"/>
       <c r="B96" s="122"/>
       <c r="C96" s="34"/>
@@ -8434,7 +8428,7 @@
       <c r="N96" s="34"/>
       <c r="O96" s="34"/>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A97" s="125"/>
       <c r="B97" s="122"/>
       <c r="C97" s="34"/>
@@ -8463,7 +8457,7 @@
       <c r="N97" s="34"/>
       <c r="O97" s="34"/>
     </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A98" s="125"/>
       <c r="B98" s="122"/>
       <c r="C98" s="34"/>
@@ -8492,7 +8486,7 @@
       <c r="N98" s="34"/>
       <c r="O98" s="34"/>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A99" s="125"/>
       <c r="B99" s="122"/>
       <c r="C99" s="34"/>
@@ -8521,7 +8515,7 @@
       <c r="N99" s="34"/>
       <c r="O99" s="34"/>
     </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A100" s="125"/>
       <c r="B100" s="122"/>
       <c r="C100" s="34"/>
@@ -8550,7 +8544,7 @@
       <c r="N100" s="34"/>
       <c r="O100" s="34"/>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A101" s="125"/>
       <c r="B101" s="122"/>
       <c r="C101" s="34"/>
@@ -8579,7 +8573,7 @@
       <c r="N101" s="34"/>
       <c r="O101" s="34"/>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A102" s="125"/>
       <c r="B102" s="122"/>
       <c r="C102" s="34"/>
@@ -8608,7 +8602,7 @@
       <c r="N102" s="34"/>
       <c r="O102" s="34"/>
     </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A103" s="125"/>
       <c r="B103" s="122"/>
       <c r="C103" s="34"/>
@@ -8637,7 +8631,7 @@
       <c r="N103" s="34"/>
       <c r="O103" s="34"/>
     </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A104" s="125"/>
       <c r="B104" s="122"/>
       <c r="C104" s="34"/>
@@ -8666,7 +8660,7 @@
       <c r="N104" s="34"/>
       <c r="O104" s="34"/>
     </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A105" s="125"/>
       <c r="B105" s="122"/>
       <c r="C105" s="34"/>
@@ -8695,7 +8689,7 @@
       <c r="N105" s="34"/>
       <c r="O105" s="34"/>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A106" s="125"/>
       <c r="B106" s="122"/>
       <c r="C106" s="34"/>
@@ -8724,7 +8718,7 @@
       <c r="N106" s="34"/>
       <c r="O106" s="34"/>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A107" s="125"/>
       <c r="B107" s="122"/>
       <c r="C107" s="34"/>
@@ -8753,7 +8747,7 @@
       <c r="N107" s="34"/>
       <c r="O107" s="34"/>
     </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A108" s="125"/>
       <c r="B108" s="122"/>
       <c r="C108" s="34"/>
@@ -8782,7 +8776,7 @@
       <c r="N108" s="34"/>
       <c r="O108" s="34"/>
     </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A109" s="125"/>
       <c r="B109" s="122"/>
       <c r="C109" s="34"/>
@@ -8811,7 +8805,7 @@
       <c r="N109" s="34"/>
       <c r="O109" s="34"/>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A110" s="125"/>
       <c r="B110" s="122"/>
       <c r="C110" s="34"/>
@@ -8840,7 +8834,7 @@
       <c r="N110" s="34"/>
       <c r="O110" s="34"/>
     </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A111" s="125"/>
       <c r="B111" s="122"/>
       <c r="C111" s="34"/>
@@ -8869,7 +8863,7 @@
       <c r="N111" s="34"/>
       <c r="O111" s="34"/>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A112" s="125"/>
       <c r="B112" s="122"/>
       <c r="C112" s="34"/>
@@ -8898,7 +8892,7 @@
       <c r="N112" s="34"/>
       <c r="O112" s="34"/>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A113" s="125"/>
       <c r="B113" s="122"/>
       <c r="C113" s="34"/>
@@ -8927,7 +8921,7 @@
       <c r="N113" s="34"/>
       <c r="O113" s="34"/>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A114" s="125"/>
       <c r="B114" s="122"/>
       <c r="C114" s="34"/>
@@ -8956,7 +8950,7 @@
       <c r="N114" s="34"/>
       <c r="O114" s="34"/>
     </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A115" s="125"/>
       <c r="B115" s="122"/>
       <c r="C115" s="34"/>
@@ -8985,7 +8979,7 @@
       <c r="N115" s="34"/>
       <c r="O115" s="34"/>
     </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A116" s="125"/>
       <c r="B116" s="122"/>
       <c r="C116" s="34"/>
@@ -9014,7 +9008,7 @@
       <c r="N116" s="34"/>
       <c r="O116" s="34"/>
     </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A117" s="125"/>
       <c r="B117" s="122"/>
       <c r="C117" s="34"/>
@@ -9043,7 +9037,7 @@
       <c r="N117" s="34"/>
       <c r="O117" s="34"/>
     </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A118" s="125"/>
       <c r="B118" s="122"/>
       <c r="C118" s="34"/>
@@ -9072,7 +9066,7 @@
       <c r="N118" s="34"/>
       <c r="O118" s="34"/>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A119" s="125"/>
       <c r="B119" s="122"/>
       <c r="C119" s="34"/>
@@ -9101,7 +9095,7 @@
       <c r="N119" s="34"/>
       <c r="O119" s="34"/>
     </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A120" s="125"/>
       <c r="B120" s="122"/>
       <c r="C120" s="34"/>
@@ -9130,7 +9124,7 @@
       <c r="N120" s="34"/>
       <c r="O120" s="34"/>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A121" s="125"/>
       <c r="B121" s="122"/>
       <c r="C121" s="34"/>
@@ -9159,7 +9153,7 @@
       <c r="N121" s="34"/>
       <c r="O121" s="34"/>
     </row>
-    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A122" s="125"/>
       <c r="B122" s="122"/>
       <c r="C122" s="34"/>
@@ -9188,7 +9182,7 @@
       <c r="N122" s="34"/>
       <c r="O122" s="34"/>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A123" s="125"/>
       <c r="B123" s="122"/>
       <c r="C123" s="34"/>
@@ -9356,7 +9350,7 @@
       </c>
       <c r="G2" s="21">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="H2" s="54" t="e">
         <f>TEXT(WEEKDAY(每日用粉紀錄表!#REF!,1),"aaaa")</f>
